--- a/public/data/patchNote.xlsx
+++ b/public/data/patchNote.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAC0EC93-FFBA-4A45-AEAA-670B3730BE47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408B2CFF-683F-4B15-817D-8FADE7C7F4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="日本語" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="90">
   <si>
     <t>title</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -472,7 +472,203 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>プロフィール画面にゲームアカウントのタブが追加されます。</t>
+    <t>2025-12-24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>修改了</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经验值和等级的计算方法</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>。&lt;br/&gt;&lt;br/&gt;&lt;p style='padding-left: 1vw'&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>等级：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>现在固定变成【？？】</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>&lt;/p&gt;&lt;p style='padding-left: 1vw'&gt;&lt;br/&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>经验值：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>今日访问量小于99的时候：今日访问量 / 99</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>今日访问量大于等于99的时候：今日访问量 / 过去一年总访问量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>&lt;/p&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>経験値・レベルの計算方法が変更されます。&lt;br/&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br/&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>&lt;p style='padding-left: 1vw'&gt;レベル：&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;固定で【？？】になります&lt;/p&gt;&lt;p style='padding-left: 1vw'&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br/&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>経験値：&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;本日の訪問者数が99未満の場合：本日の訪問者数 / 99&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;本日の訪問者数が99を超えたの場合：本日の訪問者数 / 過去一年間の総訪問者数&lt;/p&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>Changed the calculate method of EXP and Level.&lt;br/&gt;</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>&lt;br/&gt;&lt;p style='padding-left: 1vw'&gt;Level:&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;Now fixed as 【??】&lt;/p&gt;&lt;p style='padding-left: 1vw'&gt;&lt;br/&gt;Experience points:&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;When today's visits are below 99: today's visits / 99&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;When today's visits are 99 or more: today's visits / total visits in the past year&lt;/p&gt;</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026-03-01</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ミッション画面に「鉄道・旅行」のタブが追加されます。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -487,7 +683,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>页面增加了游戏账号的展示标签</t>
+      <t>页面增加了「游戏账号」的展示标签</t>
     </r>
     <r>
       <rPr>
@@ -502,16 +698,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2025-12-24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Added Game Account tab in the profile page.</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>修改了</t>
+    <r>
+      <t>在</t>
     </r>
     <r>
       <rPr>
@@ -521,7 +709,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>经验值和等级的计算方法</t>
+      <t>任务</t>
     </r>
     <r>
       <rPr>
@@ -531,7 +719,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>。&lt;br/&gt;&lt;br/&gt;&lt;p style='padding-left: 1vw'&gt;</t>
+      <t>画面追加了「</t>
     </r>
     <r>
       <rPr>
@@ -541,7 +729,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>等级：</t>
+      <t>铁道</t>
     </r>
     <r>
       <rPr>
@@ -551,7 +739,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;</t>
+      <t>・旅行」的</t>
     </r>
     <r>
       <rPr>
@@ -561,7 +749,7 @@
         <family val="2"/>
         <charset val="134"/>
       </rPr>
-      <t>现在固定变成【？？】</t>
+      <t>标签</t>
     </r>
     <r>
       <rPr>
@@ -571,130 +759,20 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t>&lt;/p&gt;&lt;p style='padding-left: 1vw'&gt;&lt;br/&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>经验值：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>今日访问量小于99的时候：今日访问量 / 99</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>今日访问量大于等于99的时候：今日访问量 / 过去一年总访问量</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>&lt;/p&gt;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>経験値・レベルの計算方法が変更されます。&lt;br/&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br/&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>&lt;p style='padding-left: 1vw'&gt;レベル：&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;固定で【？？】になります&lt;/p&gt;&lt;p style='padding-left: 1vw'&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br/&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Yu Gothic"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>経験値：&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;本日の訪問者数が99未満の場合：本日の訪問者数 / 99&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;本日の訪問者数が99を超えたの場合：本日の訪問者数 / 過去一年間の総訪問者数&lt;/p&gt;</t>
-    </r>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>Changed the calculate method of EXP and Level.&lt;br/&gt;</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>&lt;br/&gt;&lt;p style='padding-left: 1vw'&gt;Level:&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;Now fixed as 【??】&lt;/p&gt;&lt;p style='padding-left: 1vw'&gt;&lt;br/&gt;Experience points:&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;When today's visits are below 99: today's visits / 99&lt;/p&gt;&lt;p style='padding-left: 2vw'&gt;When today's visits are 99 or more: today's visits / total visits in the past year&lt;/p&gt;</t>
-    </r>
+      <t>。</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Added 「Game Account」 tab in the profile page.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Added 「Railways・Travel」 tab in the tasks page.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>プロフィール画面に「ゲームアカウント」のタブが追加されます。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1089,7 +1167,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.875" style="3" customWidth="1"/>
@@ -1107,169 +1185,177 @@
     </row>
     <row r="2" spans="1:2" ht="48.6" customHeight="1">
       <c r="A2" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="48.6" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="78.75" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>81</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="78.75" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="48.6" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="48.6" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="48.6" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="48.6" customHeight="1">
       <c r="A7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="48.6" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>63</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="48.6" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="48.6" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="48.6" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="48.6" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="47.45" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:2" ht="47.45" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="67.150000000000006" customHeight="1">
-      <c r="A12" s="5" t="s">
+    <row r="13" spans="1:2" ht="67.150000000000006" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="78" customHeight="1">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:2" ht="78" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="34.9" customHeight="1">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:2" ht="34.9" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:2" ht="34.15" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="49.9" customHeight="1">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:2" ht="49.9" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:2" ht="30" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="33.6" customHeight="1">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:2" ht="33.6" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="104.45" customHeight="1">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:2" ht="104.45" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="58.15" customHeight="1">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:2" ht="58.15" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B21" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="81.599999999999994" customHeight="1">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:2" ht="81.599999999999994" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="37.15" customHeight="1">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:2" ht="37.15" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1281,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6AFACB5-61BF-4FE7-B257-EDC62EBAA566}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.875" style="3" customWidth="1"/>
@@ -1299,169 +1385,177 @@
     </row>
     <row r="2" spans="1:2" ht="48.6" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="48.6" customHeight="1">
       <c r="A3" s="5" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="48.6" customHeight="1">
       <c r="A4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="48.6" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>73</v>
+        <v>71</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="48.6" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>66</v>
+        <v>68</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="48.6" customHeight="1">
       <c r="A7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="48.6" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>61</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="48.6" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="48.6" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="48.6" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="48.6" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="47.45" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:2" ht="47.45" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="67.150000000000006" customHeight="1">
-      <c r="A12" s="5" t="s">
+    <row r="13" spans="1:2" ht="67.150000000000006" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="78" customHeight="1">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:2" ht="78" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="34.9" customHeight="1">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:2" ht="34.9" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:2" ht="34.15" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="49.9" customHeight="1">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:2" ht="49.9" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:2" ht="30" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="33.6" customHeight="1">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:2" ht="33.6" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="104.45" customHeight="1">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:2" ht="104.45" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="58.15" customHeight="1">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:2" ht="58.15" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B21" s="4" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="81.599999999999994" customHeight="1">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:2" ht="81.599999999999994" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="37.15" customHeight="1">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:2" ht="37.15" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>37</v>
       </c>
     </row>
@@ -1473,7 +1567,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D4D9942-3D26-40C7-A8A0-986B7A52B1B6}">
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B23"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.875" style="3" customWidth="1"/>
@@ -1491,169 +1585,177 @@
     </row>
     <row r="2" spans="1:2" ht="48.6" customHeight="1">
       <c r="A2" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="48.6" customHeight="1">
+      <c r="A3" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="63.75" customHeight="1">
+      <c r="A4" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" ht="63.75" customHeight="1">
-      <c r="A3" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" ht="48.6" customHeight="1">
-      <c r="A4" s="5" t="s">
-        <v>71</v>
-      </c>
-      <c r="B4" s="6" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="48.6" customHeight="1">
       <c r="A5" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>70</v>
+        <v>71</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="48.6" customHeight="1">
       <c r="A6" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="48.6" customHeight="1">
       <c r="A7" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" ht="48.6" customHeight="1">
+      <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B8" s="4" t="s">
         <v>62</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" ht="48.6" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="48.6" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="48.6" customHeight="1">
       <c r="A10" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" ht="48.6" customHeight="1">
+      <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B11" s="4" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:2" ht="47.45" customHeight="1">
-      <c r="A11" s="2" t="s">
+    <row r="12" spans="1:2" ht="47.45" customHeight="1">
+      <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="12" spans="1:2" ht="67.150000000000006" customHeight="1">
-      <c r="A12" s="5" t="s">
+    <row r="13" spans="1:2" ht="67.150000000000006" customHeight="1">
+      <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B13" s="4" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:2" ht="78" customHeight="1">
-      <c r="A13" s="2" t="s">
+    <row r="14" spans="1:2" ht="78" customHeight="1">
+      <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B14" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:2" ht="34.9" customHeight="1">
-      <c r="A14" s="2" t="s">
+    <row r="15" spans="1:2" ht="34.9" customHeight="1">
+      <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:2" ht="34.15" customHeight="1">
-      <c r="A15" s="2" t="s">
+    <row r="16" spans="1:2" ht="34.15" customHeight="1">
+      <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="3" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:2" ht="49.9" customHeight="1">
-      <c r="A16" s="2" t="s">
+    <row r="17" spans="1:2" ht="49.9" customHeight="1">
+      <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B17" s="4" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="1:2" ht="30" customHeight="1">
-      <c r="A17" s="2" t="s">
+    <row r="18" spans="1:2" ht="30" customHeight="1">
+      <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="3" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="18" spans="1:2" ht="33.6" customHeight="1">
-      <c r="A18" s="2" t="s">
+    <row r="19" spans="1:2" ht="33.6" customHeight="1">
+      <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="3" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:2" ht="104.45" customHeight="1">
-      <c r="A19" s="2" t="s">
+    <row r="20" spans="1:2" ht="104.45" customHeight="1">
+      <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B20" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="20" spans="1:2" ht="58.15" customHeight="1">
-      <c r="A20" s="2" t="s">
+    <row r="21" spans="1:2" ht="58.15" customHeight="1">
+      <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B21" s="4" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:2" ht="81.599999999999994" customHeight="1">
-      <c r="A21" s="2" t="s">
+    <row r="22" spans="1:2" ht="81.599999999999994" customHeight="1">
+      <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B22" s="4" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:2" ht="37.15" customHeight="1">
-      <c r="A22" s="2" t="s">
+    <row r="23" spans="1:2" ht="37.15" customHeight="1">
+      <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="3" t="s">
         <v>50</v>
       </c>
     </row>

--- a/public/data/patchNote.xlsx
+++ b/public/data/patchNote.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\9_projects\BA-style-homepage\public\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{408B2CFF-683F-4B15-817D-8FADE7C7F4D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE90262B-9C78-4FA3-8A9B-E7EC2B272370}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="90">
   <si>
     <t>title</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1167,196 +1167,334 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="21.875" style="3" customWidth="1"/>
-    <col min="2" max="2" width="133" style="3" customWidth="1"/>
-    <col min="3" max="16384" width="8.875" style="3"/>
+    <col min="2" max="4" width="133" style="3" customWidth="1"/>
+    <col min="5" max="16384" width="8.875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="1" customFormat="1" ht="16.149999999999999" customHeight="1">
+    <row r="1" spans="1:4" s="1" customFormat="1" ht="16.149999999999999" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="48.6" customHeight="1">
       <c r="A2" s="5" t="s">
         <v>83</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C2" s="6" t="s">
+        <v>86</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="48.6" customHeight="1">
       <c r="A3" s="5" t="s">
         <v>79</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="78.75" customHeight="1">
+      <c r="C3" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="78.75" customHeight="1">
       <c r="A4" s="5" t="s">
         <v>76</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C4" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="48.6" customHeight="1">
       <c r="A5" s="5" t="s">
         <v>71</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C5" s="9" t="s">
+        <v>75</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="48.6" customHeight="1">
       <c r="A6" s="5" t="s">
         <v>68</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C6" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="48.6" customHeight="1">
       <c r="A7" s="5" t="s">
         <v>64</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C7" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="48.6" customHeight="1">
       <c r="A8" s="5" t="s">
         <v>60</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C8" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="48.6" customHeight="1">
       <c r="A9" s="2" t="s">
         <v>56</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="48.6" customHeight="1">
       <c r="A10" s="2" t="s">
         <v>52</v>
       </c>
       <c r="B10" s="4" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" ht="48.6" customHeight="1">
+      <c r="C10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="48.6" customHeight="1">
       <c r="A11" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="47.45" customHeight="1">
+      <c r="C11" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="47.45" customHeight="1">
       <c r="A12" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" ht="67.150000000000006" customHeight="1">
+      <c r="C12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="67.150000000000006" customHeight="1">
       <c r="A13" s="5" t="s">
         <v>6</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="78" customHeight="1">
+      <c r="C13" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="78" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="34.9" customHeight="1">
+      <c r="C14" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="34.9" customHeight="1">
       <c r="A15" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="34.15" customHeight="1">
+      <c r="C15" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="34.15" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" ht="49.9" customHeight="1">
+      <c r="C16" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="49.9" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="30" customHeight="1">
+      <c r="C17" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="30" customHeight="1">
       <c r="A18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" ht="33.6" customHeight="1">
+      <c r="C18" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" ht="33.6" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="104.45" customHeight="1">
+      <c r="C19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" ht="104.45" customHeight="1">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="21" spans="1:2" ht="58.15" customHeight="1">
+      <c r="C20" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" ht="58.15" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="22" spans="1:2" ht="81.599999999999994" customHeight="1">
+      <c r="C21" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="81.599999999999994" customHeight="1">
       <c r="A22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B22" s="4" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="1:2" ht="37.15" customHeight="1">
+      <c r="C22" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" ht="37.15" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>25</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
